--- a/02_DIA_inicio_2026_analisis_assets/rbd_9446_escuela-de-parvulos-rayito-de-luz_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9446_escuela-de-parvulos-rayito-de-luz_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC45970A-3754-429E-816E-79B775101BAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{318D16FD-1BBB-42D4-A690-1C412B30A7E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B11133B-5461-4A04-BE8A-C8B154D10E5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70EED78F-022D-45D9-8084-70CC8EE79780}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC6AE5E7-9B57-422A-A325-1364301323BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7216C8E-B237-4A8D-B5F1-B4BBB1C9F333}"/>
 </file>